--- a/Personal Budget pt-br.xlsx
+++ b/Personal Budget pt-br.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEADF864-A4E0-48C4-A5D4-9112753CCA02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96551B24-041A-4F81-9A1C-88D9472BC53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -851,13 +851,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -9992,7 +9992,7 @@
         <v>C. Crédito</v>
       </c>
       <c r="C13" s="26">
-        <f>SUMIF(Tabela1[Conta],B13,Tabela1[Valor])-SUMIF(Tabela1[Categoria],B13,Tabela1[Valor])</f>
+        <f ca="1">SUMIF(Tabela1[Conta],B13,Tabela1[Valor])-SUMIFS(Tabela1[Valor],Tabela1[Categoria],B13,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E13" s="69" t="str">
@@ -10098,7 +10098,7 @@
       <c r="H19" s="36"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="88"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="33" t="str">
         <f t="shared" ref="C20" si="1">IF(ISBLANK(B20),"",PROPER(TEXT(B20,"MMMM")))</f>
         <v/>
@@ -15664,15 +15664,15 @@
         <v>41</v>
       </c>
       <c r="J2" s="3"/>
-      <c r="K2" s="86" t="s">
+      <c r="K2" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="87"/>
+      <c r="L2" s="88"/>
       <c r="M2" s="37"/>
-      <c r="N2" s="86" t="s">
+      <c r="N2" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="87"/>
+      <c r="O2" s="88"/>
       <c r="P2" s="38"/>
     </row>
     <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.3">

--- a/Personal Budget pt-br.xlsx
+++ b/Personal Budget pt-br.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rcssi\Code\Personal_Finance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96551B24-041A-4F81-9A1C-88D9472BC53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76FF7F9-6AD9-4E93-AD1A-29785E788F1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-114" yWindow="-114" windowWidth="19704" windowHeight="11178" tabRatio="797" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9992,7 +9992,7 @@
         <v>C. Crédito</v>
       </c>
       <c r="C13" s="26">
-        <f ca="1">SUMIF(Tabela1[Conta],B13,Tabela1[Valor])-SUMIFS(Tabela1[Valor],Tabela1[Categoria],B13,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
+        <f ca="1">SUMIFS(Tabela1[Valor],Tabela1[Conta],B13,Tabela1[Data],"&lt;="&amp;(TODAY()))-SUMIFS(Tabela1[Valor],Tabela1[Categoria],B13,Tabela1[Data],"&lt;="&amp;(TODAY()))</f>
         <v>0</v>
       </c>
       <c r="E13" s="69" t="str">
@@ -13331,7 +13331,7 @@
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="6">
+  <dataValidations disablePrompts="1" count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{60D5F252-CE9E-4A5F-916C-4BCED7BE4850}">
       <formula1>"Despesas, Receita Líquida"</formula1>
     </dataValidation>
